--- a/results/Int Task Remove ACC 0.1/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_8_permute.xlsx
@@ -440,97 +440,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7362174802689272</v>
+        <v>0.7035646538588318</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7798702631431645</v>
+        <v>0.7029215670421116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7795487197348043</v>
+        <v>0.7005087475977536</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7809944211907679</v>
+        <v>0.7005087475977536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7618712955649399</v>
+        <v>0.6990456317985907</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7834022651084975</v>
+        <v>0.7025925603438088</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7810143232972815</v>
+        <v>0.6961592044132922</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.758326854783036</v>
+        <v>0.6961542288866638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7607496252806508</v>
+        <v>0.6959897255375124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7509612095505234</v>
+        <v>0.7080413839427318</v>
       </c>
     </row>
     <row r="12">
@@ -540,237 +540,237 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7474267198218761</v>
+        <v>0.7075652882384771</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.737777929807758</v>
+        <v>0.705474012202479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7525515122491246</v>
+        <v>0.7008079011362859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7427680720456256</v>
+        <v>0.6980635872303109</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7422845130514283</v>
+        <v>0.6853588909551145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7437277267440776</v>
+        <v>0.6827940069781762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7348765758425744</v>
+        <v>0.7187819910813685</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7388971123287331</v>
+        <v>0.7271421196987319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7396997269679763</v>
+        <v>0.7547699751845609</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7138316530565283</v>
+        <v>0.7571877701555474</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7178546773060011</v>
+        <v>0.7600816608307885</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7125429916597734</v>
+        <v>0.7478878889462457</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7251080622189605</v>
+        <v>0.7493385659288375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.758094870853987</v>
+        <v>0.7408313483055222</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7641942445595726</v>
+        <v>0.7242656433666901</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7627236654704672</v>
+        <v>0.7194474677679166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7323490083153489</v>
+        <v>0.740951071915018</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7256914427161401</v>
+        <v>0.7427183167793416</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7096291988780188</v>
+        <v>0.7427183167793416</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7096291988780188</v>
+        <v>0.7747181053194598</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6523123760005474</v>
+        <v>0.7755931760652292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6756479068581416</v>
+        <v>0.7602788160734387</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6673627221106184</v>
+        <v>0.7729085684787949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6793070957229129</v>
+        <v>0.76174690739923</v>
       </c>
     </row>
     <row r="36">
@@ -780,47 +780,47 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6782951979948628</v>
+        <v>0.7723702786916853</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.653870337776064</v>
+        <v>0.7639778091512374</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6250639044201334</v>
+        <v>0.7639778091512374</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6250639044201334</v>
+        <v>0.7549845447704105</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6625097178254461</v>
+        <v>0.7191536007264269</v>
       </c>
     </row>
     <row r="41">
@@ -830,117 +830,117 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6688609775665944</v>
+        <v>0.7160578902523214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6641849154471444</v>
+        <v>0.735151162718379</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6646684744413416</v>
+        <v>0.7282917773203057</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6568142946880033</v>
+        <v>0.7325116458420146</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6568118069246891</v>
+        <v>0.7325116458420146</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6556677467705723</v>
+        <v>0.7283290937700188</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6590526597299533</v>
+        <v>0.7302658175101221</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6803193044213773</v>
+        <v>0.7626592945947123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6803193044213773</v>
+        <v>0.7192835863595937</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.686528450683202</v>
+        <v>0.6816334653921026</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6836295844813325</v>
+        <v>0.6274002251425799</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6598356832330972</v>
+        <v>0.6311166325635779</v>
       </c>
     </row>
     <row r="53">
@@ -950,377 +950,377 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6873562539260014</v>
+        <v>0.6420665227910216</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6416622612524645</v>
+        <v>0.643350208661148</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6318390168359382</v>
+        <v>0.6193268112471779</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6565900850193113</v>
+        <v>0.6004530838935983</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6565900850193113</v>
+        <v>0.5981973045084491</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6375496775236804</v>
+        <v>0.5417754544832605</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6283048380777053</v>
+        <v>0.5496694384496259</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6235438810351583</v>
+        <v>0.5881846791096295</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6442147064128319</v>
+        <v>0.5706095642060615</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6500223898698279</v>
+        <v>0.5515862600832157</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6596537655407464</v>
+        <v>0.5515862600832157</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6594892621915951</v>
+        <v>0.5572294401910602</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6504785834675688</v>
+        <v>0.5707666042652703</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6540528774092433</v>
+        <v>0.5707666042652703</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6352612462450322</v>
+        <v>0.5254765621598761</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6277111955568546</v>
+        <v>0.5317603413211267</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6415024224595272</v>
+        <v>0.5317603413211267</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6415024224595272</v>
+        <v>0.5333755216528699</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6190942053773003</v>
+        <v>0.5272587336040849</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6121698271626438</v>
+        <v>0.5272587336040849</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4991920988637141</v>
+        <v>0.5366058823163564</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.491004247855859</v>
+        <v>0.5366058823163564</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.491004247855859</v>
+        <v>0.5269371901957247</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4987362162363873</v>
+        <v>0.5291954573441883</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5001943565089217</v>
+        <v>0.5266231100773072</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4966573790169603</v>
+        <v>0.5184150459925243</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4995263920590595</v>
+        <v>0.5140729660980055</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5004935100474541</v>
+        <v>0.518731613874256</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5050199953976379</v>
+        <v>0.5230836448220316</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5032527505333143</v>
+        <v>0.5237317071653803</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4996908954082109</v>
+        <v>0.5237317071653803</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4977566594314217</v>
+        <v>0.5002938670414897</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4958298867445751</v>
+        <v>0.5002938670414897</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4966374769104467</v>
+        <v>0.4926216049805022</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5021111781425115</v>
+        <v>0.4976266737982548</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5005059488640251</v>
+        <v>0.5000597063195408</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5005059488640251</v>
+        <v>0.4990751739879468</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5041999664151953</v>
+        <v>0.5004885345208256</v>
       </c>
     </row>
   </sheetData>
